--- a/data/GA_calidad_2001_.xlsx
+++ b/data/GA_calidad_2001_.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DATOS_LIZ\TESIS\Proyecto 2024\Relevamiento_Patiño\INFORME LB\Tablas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rosario Barrios\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE73DFE-22FF-45B6-9434-37FC2790E866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13550" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{2DDF4B9E-3FFB-4EE9-8028-732187DC40D1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16815" windowHeight="7905"/>
   </bookViews>
   <sheets>
     <sheet name="GA_calidad_2001" sheetId="1" r:id="rId1"/>
@@ -23,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="173">
   <si>
     <t>No</t>
   </si>
@@ -533,18 +532,27 @@
   </si>
   <si>
     <t>Fr.Recalde San Lorenzo</t>
+  </si>
+  <si>
+    <t>CONTAMINACION</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>SI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000000000000000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1048,7 +1056,7 @@
     <cellStyle name="60% - Énfasis4" xfId="33" builtinId="44" customBuiltin="1"/>
     <cellStyle name="60% - Énfasis5" xfId="37" builtinId="48" customBuiltin="1"/>
     <cellStyle name="60% - Énfasis6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Bueno" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Buena" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Cálculo" xfId="11" builtinId="22" customBuiltin="1"/>
     <cellStyle name="Celda de comprobación" xfId="13" builtinId="23" customBuiltin="1"/>
     <cellStyle name="Celda vinculada" xfId="12" builtinId="24" customBuiltin="1"/>
@@ -1402,38 +1410,39 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C73F51A5-8E79-45B3-90D0-D1157123E36A}">
-  <dimension ref="A1:AD68"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AE68"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.75" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="21.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.28515625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.25" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.25" style="2" customWidth="1"/>
+    <col min="8" max="8" width="14.625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.75" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.75" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="18.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="18.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="17.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="19.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="19.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="18.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="18.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="8.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="19.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.875" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1524,8 +1533,11 @@
       <c r="AD1" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="AE1" s="1" t="s">
+        <v>170</v>
+      </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1616,8 +1628,11 @@
       <c r="AD2" s="1">
         <v>0</v>
       </c>
+      <c r="AE2" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1708,8 +1723,11 @@
       <c r="AD3" s="1">
         <v>1200</v>
       </c>
+      <c r="AE3" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1800,8 +1818,11 @@
       <c r="AD4" s="1">
         <v>0</v>
       </c>
+      <c r="AE4" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31">
       <c r="A5" s="1">
         <v>10</v>
       </c>
@@ -1892,8 +1913,11 @@
       <c r="AD5" s="1">
         <v>1</v>
       </c>
+      <c r="AE5" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31">
       <c r="A6" s="1">
         <v>11</v>
       </c>
@@ -1984,8 +2008,11 @@
       <c r="AD6" s="1">
         <v>5</v>
       </c>
+      <c r="AE6" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31">
       <c r="A7" s="1">
         <v>12</v>
       </c>
@@ -2076,8 +2103,11 @@
       <c r="AD7" s="1">
         <v>0</v>
       </c>
+      <c r="AE7" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31">
       <c r="A8" s="1">
         <v>13</v>
       </c>
@@ -2168,8 +2198,11 @@
       <c r="AD8" s="1">
         <v>0</v>
       </c>
+      <c r="AE8" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31">
       <c r="A9" s="1">
         <v>22</v>
       </c>
@@ -2257,8 +2290,11 @@
       <c r="AD9" s="1">
         <v>0</v>
       </c>
+      <c r="AE9" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31">
       <c r="A10" s="1">
         <v>25</v>
       </c>
@@ -2346,8 +2382,11 @@
       <c r="AD10" s="1">
         <v>150</v>
       </c>
+      <c r="AE10" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31">
       <c r="A11" s="1">
         <v>29</v>
       </c>
@@ -2435,8 +2474,11 @@
       <c r="AD11" s="1">
         <v>0</v>
       </c>
+      <c r="AE11" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31">
       <c r="A12" s="1">
         <v>30</v>
       </c>
@@ -2524,8 +2566,11 @@
       <c r="AD12" s="1">
         <v>0</v>
       </c>
+      <c r="AE12" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31">
       <c r="A13" s="1">
         <v>31</v>
       </c>
@@ -2613,8 +2658,11 @@
       <c r="AD13" s="1">
         <v>0</v>
       </c>
+      <c r="AE13" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31">
       <c r="A14" s="1">
         <v>32</v>
       </c>
@@ -2702,8 +2750,11 @@
       <c r="AD14" s="1">
         <v>0</v>
       </c>
+      <c r="AE14" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31">
       <c r="A15" s="1">
         <v>33</v>
       </c>
@@ -2791,8 +2842,11 @@
       <c r="AD15" s="1">
         <v>0</v>
       </c>
+      <c r="AE15" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31">
       <c r="A16" s="1">
         <v>34</v>
       </c>
@@ -2880,8 +2934,11 @@
       <c r="AD16" s="1">
         <v>4</v>
       </c>
+      <c r="AE16" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31">
       <c r="A17" s="1">
         <v>35</v>
       </c>
@@ -2969,8 +3026,11 @@
       <c r="AD17" s="1">
         <v>2</v>
       </c>
+      <c r="AE17" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31">
       <c r="A18" s="1">
         <v>36</v>
       </c>
@@ -3056,8 +3116,11 @@
       <c r="AD18" s="1">
         <v>20</v>
       </c>
+      <c r="AE18" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31">
       <c r="A19" s="1">
         <v>37</v>
       </c>
@@ -3143,8 +3206,11 @@
       <c r="AD19" s="1">
         <v>830</v>
       </c>
+      <c r="AE19" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31">
       <c r="A20" s="1">
         <v>38</v>
       </c>
@@ -3232,8 +3298,11 @@
       <c r="AD20" s="1">
         <v>0</v>
       </c>
+      <c r="AE20" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31">
       <c r="A21" s="1">
         <v>39</v>
       </c>
@@ -3321,8 +3390,11 @@
       <c r="AD21" s="1">
         <v>4</v>
       </c>
+      <c r="AE21" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31">
       <c r="A22" s="1">
         <v>40</v>
       </c>
@@ -3410,8 +3482,11 @@
       <c r="AD22" s="1">
         <v>2</v>
       </c>
+      <c r="AE22" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31">
       <c r="A23" s="1">
         <v>41</v>
       </c>
@@ -3499,8 +3574,11 @@
       <c r="AD23" s="1">
         <v>5</v>
       </c>
+      <c r="AE23" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31">
       <c r="A24" s="1">
         <v>42</v>
       </c>
@@ -3588,8 +3666,11 @@
       <c r="AD24" s="1">
         <v>67</v>
       </c>
+      <c r="AE24" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31">
       <c r="A25" s="1">
         <v>47</v>
       </c>
@@ -3677,8 +3758,11 @@
       <c r="AD25" s="1">
         <v>1</v>
       </c>
+      <c r="AE25" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31">
       <c r="A26" s="1">
         <v>48</v>
       </c>
@@ -3766,8 +3850,11 @@
       <c r="AD26" s="1">
         <v>1</v>
       </c>
+      <c r="AE26" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31">
       <c r="A27" s="1">
         <v>54</v>
       </c>
@@ -3856,8 +3943,11 @@
       <c r="AD27" s="1">
         <v>130</v>
       </c>
+      <c r="AE27" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:31">
       <c r="A28" s="1">
         <v>55</v>
       </c>
@@ -3946,8 +4036,11 @@
       <c r="AD28" s="1">
         <v>0</v>
       </c>
+      <c r="AE28" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:31">
       <c r="A29" s="1">
         <v>56</v>
       </c>
@@ -4036,8 +4129,11 @@
       <c r="AD29" s="1">
         <v>44</v>
       </c>
+      <c r="AE29" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:31">
       <c r="A30" s="1">
         <v>57</v>
       </c>
@@ -4126,8 +4222,11 @@
       <c r="AD30" s="1">
         <v>0</v>
       </c>
+      <c r="AE30" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:31">
       <c r="A31" s="1">
         <v>58</v>
       </c>
@@ -4216,8 +4315,11 @@
       <c r="AD31" s="1">
         <v>10000</v>
       </c>
+      <c r="AE31" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31">
       <c r="A32" s="1">
         <v>59</v>
       </c>
@@ -4306,8 +4408,11 @@
       <c r="AD32" s="1">
         <v>2</v>
       </c>
+      <c r="AE32" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:31">
       <c r="A33" s="1">
         <v>60</v>
       </c>
@@ -4396,8 +4501,11 @@
       <c r="AD33" s="1">
         <v>0</v>
       </c>
+      <c r="AE33" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:31">
       <c r="A34" s="1">
         <v>61</v>
       </c>
@@ -4483,8 +4591,11 @@
       <c r="AD34" s="1">
         <v>0</v>
       </c>
+      <c r="AE34" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:31">
       <c r="A35" s="1">
         <v>62</v>
       </c>
@@ -4570,8 +4681,11 @@
       <c r="AD35" s="1">
         <v>10</v>
       </c>
+      <c r="AE35" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:31">
       <c r="A36" s="1">
         <v>69</v>
       </c>
@@ -4657,8 +4771,11 @@
       <c r="AD36" s="1">
         <v>0</v>
       </c>
+      <c r="AE36" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:31">
       <c r="A37" s="1">
         <v>70</v>
       </c>
@@ -4747,8 +4864,11 @@
       <c r="AD37" s="1">
         <v>103</v>
       </c>
+      <c r="AE37" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:31">
       <c r="A38" s="1">
         <v>71</v>
       </c>
@@ -4837,8 +4957,11 @@
       <c r="AD38" s="1">
         <v>0</v>
       </c>
+      <c r="AE38" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:31">
       <c r="A39" s="1">
         <v>72</v>
       </c>
@@ -4927,8 +5050,11 @@
       <c r="AD39" s="1">
         <v>380</v>
       </c>
+      <c r="AE39" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:31">
       <c r="A40" s="1">
         <v>83</v>
       </c>
@@ -5016,8 +5142,11 @@
       <c r="AD40" s="1">
         <v>276</v>
       </c>
+      <c r="AE40" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:31">
       <c r="A41" s="1">
         <v>84</v>
       </c>
@@ -5105,8 +5234,11 @@
       <c r="AD41" s="1">
         <v>7400</v>
       </c>
+      <c r="AE41" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:31">
       <c r="A42" s="1">
         <v>85</v>
       </c>
@@ -5194,8 +5326,11 @@
       <c r="AD42" s="1">
         <v>3200</v>
       </c>
+      <c r="AE42" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:31">
       <c r="A43" s="1">
         <v>86</v>
       </c>
@@ -5283,8 +5418,11 @@
       <c r="AD43" s="1">
         <v>765</v>
       </c>
+      <c r="AE43" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:31">
       <c r="A44" s="1">
         <v>87</v>
       </c>
@@ -5372,8 +5510,11 @@
       <c r="AD44" s="1">
         <v>30</v>
       </c>
+      <c r="AE44" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:31">
       <c r="A45" s="1">
         <v>88</v>
       </c>
@@ -5461,8 +5602,11 @@
       <c r="AD45" s="1">
         <v>6</v>
       </c>
+      <c r="AE45" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:31">
       <c r="A46" s="1">
         <v>90</v>
       </c>
@@ -5550,8 +5694,11 @@
       <c r="AD46" s="1">
         <v>1410</v>
       </c>
+      <c r="AE46" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:31">
       <c r="A47" s="1">
         <v>91</v>
       </c>
@@ -5639,8 +5786,11 @@
       <c r="AD47" s="1">
         <v>18</v>
       </c>
+      <c r="AE47" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:31">
       <c r="A48" s="1">
         <v>92</v>
       </c>
@@ -5728,8 +5878,11 @@
       <c r="AD48" s="1">
         <v>0</v>
       </c>
+      <c r="AE48" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:31">
       <c r="A49" s="1">
         <v>93</v>
       </c>
@@ -5815,8 +5968,11 @@
       <c r="AD49" s="1">
         <v>2560</v>
       </c>
+      <c r="AE49" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:31">
       <c r="A50" s="1">
         <v>94</v>
       </c>
@@ -5902,8 +6058,11 @@
       <c r="AD50" s="1">
         <v>6</v>
       </c>
+      <c r="AE50" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:31">
       <c r="A51" s="1">
         <v>95</v>
       </c>
@@ -5989,8 +6148,11 @@
       <c r="AD51" s="1">
         <v>3825</v>
       </c>
+      <c r="AE51" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:31">
       <c r="A52" s="1">
         <v>99</v>
       </c>
@@ -6078,8 +6240,11 @@
       <c r="AD52" s="1">
         <v>3</v>
       </c>
+      <c r="AE52" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:31">
       <c r="A53" s="1">
         <v>100</v>
       </c>
@@ -6167,8 +6332,11 @@
       <c r="AD53" s="1">
         <v>610</v>
       </c>
+      <c r="AE53" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:31">
       <c r="A54" s="1">
         <v>101</v>
       </c>
@@ -6256,8 +6424,11 @@
       <c r="AD54" s="1">
         <v>20</v>
       </c>
+      <c r="AE54" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="55" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:31">
       <c r="A55" s="1">
         <v>102</v>
       </c>
@@ -6345,8 +6516,11 @@
       <c r="AD55" s="1">
         <v>29</v>
       </c>
+      <c r="AE55" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="56" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:31">
       <c r="A56" s="1">
         <v>103</v>
       </c>
@@ -6434,8 +6608,11 @@
       <c r="AD56" s="1">
         <v>40</v>
       </c>
+      <c r="AE56" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="57" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:31">
       <c r="A57" s="1">
         <v>104</v>
       </c>
@@ -6523,8 +6700,11 @@
       <c r="AD57" s="1">
         <v>15</v>
       </c>
+      <c r="AE57" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="58" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:31">
       <c r="A58" s="1">
         <v>105</v>
       </c>
@@ -6612,8 +6792,11 @@
       <c r="AD58" s="1">
         <v>132</v>
       </c>
+      <c r="AE58" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:31">
       <c r="A59" s="1">
         <v>106</v>
       </c>
@@ -6699,8 +6882,11 @@
       <c r="AD59" s="1">
         <v>61200</v>
       </c>
+      <c r="AE59" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="60" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:31">
       <c r="A60" s="1">
         <v>107</v>
       </c>
@@ -6786,8 +6972,11 @@
       <c r="AD60" s="1">
         <v>2</v>
       </c>
+      <c r="AE60" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="61" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:31">
       <c r="A61" s="1">
         <v>108</v>
       </c>
@@ -6873,8 +7062,11 @@
       <c r="AD61" s="1">
         <v>25</v>
       </c>
+      <c r="AE61" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="62" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:31">
       <c r="A62" s="1">
         <v>109</v>
       </c>
@@ -6960,8 +7152,11 @@
       <c r="AD62" s="1">
         <v>5</v>
       </c>
+      <c r="AE62" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="63" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:31">
       <c r="A63" s="1">
         <v>110</v>
       </c>
@@ -7049,8 +7244,11 @@
       <c r="AD63" s="1">
         <v>45900</v>
       </c>
+      <c r="AE63" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="64" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:31">
       <c r="A64" s="1">
         <v>111</v>
       </c>
@@ -7138,8 +7336,11 @@
       <c r="AD64" s="1">
         <v>15300</v>
       </c>
+      <c r="AE64" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="65" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:31">
       <c r="A65" s="1">
         <v>112</v>
       </c>
@@ -7227,8 +7428,11 @@
       <c r="AD65" s="1">
         <v>18360</v>
       </c>
+      <c r="AE65" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="66" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:31">
       <c r="A66" s="1">
         <v>113</v>
       </c>
@@ -7316,8 +7520,11 @@
       <c r="AD66" s="1">
         <v>2295</v>
       </c>
+      <c r="AE66" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="67" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:31">
       <c r="A67" s="1">
         <v>114</v>
       </c>
@@ -7405,8 +7612,11 @@
       <c r="AD67" s="1">
         <v>238</v>
       </c>
+      <c r="AE67" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:31">
       <c r="A68" s="1">
         <v>115</v>
       </c>
@@ -7493,6 +7703,9 @@
       </c>
       <c r="AD68" s="1">
         <v>0</v>
+      </c>
+      <c r="AE68" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>
